--- a/data/trans_camb/P3A_R1-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R1-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 13,74</t>
+          <t>1,32; 14,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 18,0</t>
+          <t>6,43; 19,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 16,94</t>
+          <t>4,09; 17,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 9,67</t>
+          <t>-4,9; 9,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 11,4</t>
+          <t>-2,91; 11,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 11,31</t>
+          <t>-0,89; 11,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 10,61</t>
+          <t>0,29; 10,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 13,75</t>
+          <t>3,87; 13,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,62</t>
+          <t>3,66; 12,18</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 54,45</t>
+          <t>4,51; 59,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,04; 72,01</t>
+          <t>20,71; 77,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,66; 68,44</t>
+          <t>15,15; 71,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 39,17</t>
+          <t>-15,79; 39,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 47,64</t>
+          <t>-9,34; 45,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 46,4</t>
+          <t>-2,96; 49,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 39,91</t>
+          <t>0,96; 39,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,99; 53,9</t>
+          <t>12,22; 52,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 49,69</t>
+          <t>11,97; 47,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 15,18</t>
+          <t>1,77; 15,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,14; 26,57</t>
+          <t>13,08; 27,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 14,4</t>
+          <t>-0,06; 13,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 7,24</t>
+          <t>-5,51; 7,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 15,9</t>
+          <t>3,54; 16,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 10,74</t>
+          <t>-0,61; 11,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,34</t>
+          <t>0,6; 10,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 19,54</t>
+          <t>10,19; 19,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 11,04</t>
+          <t>2,04; 10,73</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 63,37</t>
+          <t>5,77; 63,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,0; 108,17</t>
+          <t>42,63; 117,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 59,16</t>
+          <t>-0,2; 53,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 35,75</t>
+          <t>-21,11; 35,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 79,65</t>
+          <t>13,85; 83,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 53,04</t>
+          <t>-1,96; 57,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 44,4</t>
+          <t>2,23; 46,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,29; 85,07</t>
+          <t>36,92; 85,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 49,08</t>
+          <t>7,22; 46,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,28</t>
+          <t>1,55; 12,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 18,73</t>
+          <t>7,86; 19,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 8,79</t>
+          <t>-17,3; 9,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 13,93</t>
+          <t>0,62; 14,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 24,35</t>
+          <t>6,78; 24,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 19,16</t>
+          <t>4,37; 19,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 11,01</t>
+          <t>2,12; 10,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 18,21</t>
+          <t>8,5; 18,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 9,43</t>
+          <t>-13,04; 9,2</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 57,08</t>
+          <t>5,48; 56,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,16; 85,53</t>
+          <t>29,3; 89,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,31; 37,43</t>
+          <t>-65,26; 39,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 160,25</t>
+          <t>2,79; 180,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,19; 274,8</t>
+          <t>37,68; 276,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,1; 231,95</t>
+          <t>22,52; 229,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 56,2</t>
+          <t>8,9; 55,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,55; 95,51</t>
+          <t>35,79; 94,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,93; 44,45</t>
+          <t>-54,83; 43,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,94</t>
+          <t>2,78; 9,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,94; 18,41</t>
+          <t>10,92; 18,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 13,1</t>
+          <t>5,39; 13,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 9,57</t>
+          <t>1,52; 9,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 11,41</t>
+          <t>3,76; 10,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 15,21</t>
+          <t>-2,62; 14,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,43</t>
+          <t>3,16; 8,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,49; 13,85</t>
+          <t>8,45; 13,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 11,79</t>
+          <t>-0,05; 11,88</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,89; 54,0</t>
+          <t>12,19; 51,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>49,57; 98,91</t>
+          <t>47,97; 98,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,43; 69,84</t>
+          <t>23,33; 71,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,86; 84,15</t>
+          <t>8,94; 83,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,66; 102,25</t>
+          <t>24,16; 96,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 124,73</t>
+          <t>-17,39; 119,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,54; 51,11</t>
+          <t>16,68; 50,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,48; 84,92</t>
+          <t>44,66; 84,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 68,13</t>
+          <t>0,12; 69,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 12,38</t>
+          <t>1,38; 12,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 11,63</t>
+          <t>0,93; 11,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 12,16</t>
+          <t>0,1; 11,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 6,19</t>
+          <t>-0,13; 6,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,8</t>
+          <t>2,33; 9,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,37; 13,1</t>
+          <t>5,13; 13,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,76</t>
+          <t>1,55; 7,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,54</t>
+          <t>3,66; 9,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,26; 11,3</t>
+          <t>4,05; 11,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4,28; 89,15</t>
+          <t>6,22; 91,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3,86; 91,28</t>
+          <t>4,12; 84,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0,69; 88,15</t>
+          <t>0,29; 82,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 97,78</t>
+          <t>-0,94; 111,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,86; 139,9</t>
+          <t>23,02; 142,22</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,05; 208,81</t>
+          <t>55,53; 211,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,49; 82,56</t>
+          <t>10,94; 83,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>28,11; 97,77</t>
+          <t>27,7; 99,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>36,04; 114,2</t>
+          <t>34,62; 123,33</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,78</t>
+          <t>-1,94; 0,71</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,66</t>
+          <t>-1,11; 2,26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,68</t>
+          <t>-0,5; 5,23</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,96</t>
+          <t>-1,07; 2,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,23</t>
+          <t>1,6; 6,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,19</t>
+          <t>0,57; 4,99</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,16</t>
+          <t>-0,9; 2,5</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,8</t>
+          <t>1,36; 5,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,34</t>
+          <t>0,43; 4,37</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-93,19; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 59,78</t>
+          <t>-16,27; 55,77</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24,02; 123,8</t>
+          <t>21,85; 117,24</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,62; 101,15</t>
+          <t>7,77; 93,56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 51,45</t>
+          <t>-16,01; 60,99</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>22,37; 116,51</t>
+          <t>23,06; 121,51</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2,66; 101,55</t>
+          <t>6,71; 98,53</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,81</t>
+          <t>4,35; 8,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,92</t>
+          <t>9,31; 13,95</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 9,13</t>
+          <t>-1,21; 9,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,63</t>
+          <t>1,21; 4,64</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,78; 8,19</t>
+          <t>4,88; 8,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,08; 10,3</t>
+          <t>4,58; 10,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,09</t>
+          <t>3,36; 6,03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,48</t>
+          <t>7,74; 10,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,17</t>
+          <t>3,91; 9,17</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>19,58; 44,07</t>
+          <t>19,95; 44,57</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>42,05; 69,91</t>
+          <t>42,39; 70,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 45,01</t>
+          <t>-4,42; 45,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,72; 42,52</t>
+          <t>9,66; 41,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>36,37; 73,27</t>
+          <t>37,88; 74,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,48; 91,32</t>
+          <t>38,03; 90,89</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,5; 38,11</t>
+          <t>19,75; 37,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>44,69; 66,56</t>
+          <t>45,08; 65,78</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>24,04; 57,29</t>
+          <t>23,37; 56,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R1-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R1-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,82</t>
+          <t>10,94</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,23</t>
+          <t>7,95</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 14,65</t>
+          <t>0,73; 14,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 19,19</t>
+          <t>4,89; 18,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 17,11</t>
+          <t>5,08; 16,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 9,86</t>
+          <t>-5,99; 9,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 11,07</t>
+          <t>-2,8; 11,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 11,81</t>
+          <t>-2,23; 10,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 10,2</t>
+          <t>1,11; 10,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 13,65</t>
+          <t>3,81; 13,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 12,18</t>
+          <t>3,55; 12,06</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 59,94</t>
+          <t>2,02; 55,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,71; 77,47</t>
+          <t>15,47; 73,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,15; 71,59</t>
+          <t>15,97; 67,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 39,94</t>
+          <t>-18,03; 36,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 45,97</t>
+          <t>-9,13; 44,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 49,1</t>
+          <t>-6,43; 44,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 39,94</t>
+          <t>3,6; 41,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,22; 52,92</t>
+          <t>12,69; 51,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,97; 47,8</t>
+          <t>11,56; 47,32</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,84</t>
+          <t>7,16</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>4,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,38</t>
+          <t>6,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 15,58</t>
+          <t>1,59; 15,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 27,77</t>
+          <t>12,1; 27,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 13,0</t>
+          <t>0,41; 13,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 7,18</t>
+          <t>-6,2; 7,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 16,42</t>
+          <t>2,61; 16,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 11,45</t>
+          <t>-1,91; 10,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 10,41</t>
+          <t>-0,09; 9,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 19,78</t>
+          <t>9,94; 19,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 10,73</t>
+          <t>1,54; 10,56</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 63,3</t>
+          <t>4,37; 62,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,63; 117,09</t>
+          <t>37,89; 111,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 53,32</t>
+          <t>0,84; 53,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 35,85</t>
+          <t>-22,72; 38,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,85; 83,75</t>
+          <t>10,36; 83,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 57,13</t>
+          <t>-7,1; 51,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 46,68</t>
+          <t>-0,57; 42,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,92; 85,94</t>
+          <t>36,42; 84,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 46,3</t>
+          <t>5,64; 46,8</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,45</t>
+          <t>6,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,12</t>
+          <t>11,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>7,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,28</t>
+          <t>1,66; 11,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,86; 19,03</t>
+          <t>7,82; 19,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 9,57</t>
+          <t>1,2; 12,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 14,41</t>
+          <t>1,39; 14,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 24,26</t>
+          <t>6,77; 23,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 19,67</t>
+          <t>4,93; 19,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 10,55</t>
+          <t>1,96; 10,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,5; 18,21</t>
+          <t>8,82; 18,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 9,2</t>
+          <t>3,22; 12,76</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-18,02%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-3,14%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 56,26</t>
+          <t>6,5; 53,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,3; 89,65</t>
+          <t>28,99; 87,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 39,92</t>
+          <t>3,53; 57,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,79; 180,35</t>
+          <t>6,68; 174,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,68; 276,98</t>
+          <t>36,9; 273,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,52; 229,89</t>
+          <t>27,73; 224,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,9; 55,61</t>
+          <t>7,63; 56,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,79; 94,49</t>
+          <t>35,47; 95,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 43,96</t>
+          <t>13,43; 65,34</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,27</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,2</t>
+          <t>13,4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>10,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,71</t>
+          <t>2,65; 10,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,92; 18,72</t>
+          <t>10,93; 18,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 13,66</t>
+          <t>5,77; 13,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 9,76</t>
+          <t>1,12; 9,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,89</t>
+          <t>3,46; 11,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 14,88</t>
+          <t>9,71; 16,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,53</t>
+          <t>3,06; 8,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,45; 13,89</t>
+          <t>8,26; 13,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 11,88</t>
+          <t>7,98; 13,2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>101,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>59,96%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,19; 51,28</t>
+          <t>11,71; 53,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47,97; 98,94</t>
+          <t>49,38; 97,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,33; 71,56</t>
+          <t>25,61; 69,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,94; 83,45</t>
+          <t>6,84; 85,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,16; 96,99</t>
+          <t>22,88; 101,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 119,32</t>
+          <t>63,24; 147,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,68; 50,66</t>
+          <t>15,75; 49,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,66; 84,25</t>
+          <t>43,02; 82,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 69,96</t>
+          <t>42,24; 81,52</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,52</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>11,15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>8,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 12,43</t>
+          <t>0,47; 11,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 11,51</t>
+          <t>0,31; 11,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 11,76</t>
+          <t>-0,93; 10,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 6,58</t>
+          <t>-0,16; 6,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,18</t>
+          <t>2,03; 8,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,13; 13,43</t>
+          <t>8,1; 14,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,94</t>
+          <t>1,73; 7,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,46</t>
+          <t>3,67; 9,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,8</t>
+          <t>5,92; 11,67</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>121,67%</t>
+          <t>143,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6,22; 91,61</t>
+          <t>1,98; 80,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,12; 84,66</t>
+          <t>1,0; 83,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0,29; 82,24</t>
+          <t>-3,83; 77,11</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 111,36</t>
+          <t>-2,8; 108,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,02; 142,22</t>
+          <t>21,36; 144,02</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,53; 211,24</t>
+          <t>79,02; 234,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,94; 83,42</t>
+          <t>13,06; 81,14</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27,7; 99,75</t>
+          <t>26,96; 98,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>34,62; 123,33</t>
+          <t>45,11; 122,3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,3</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,71</t>
+          <t>-2,01; 0,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,26</t>
+          <t>-1,04; 2,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 5,23</t>
+          <t>-0,28; 5,87</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,91</t>
+          <t>-1,28; 2,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,16</t>
+          <t>1,59; 6,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,99</t>
+          <t>0,38; 4,75</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,5</t>
+          <t>-0,97; 2,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,03</t>
+          <t>1,38; 5,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,37</t>
+          <t>0,61; 4,14</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>233,62%</t>
+          <t>278,2%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 55,77</t>
+          <t>-17,48; 54,22</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>21,85; 117,24</t>
+          <t>21,43; 120,45</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,77; 93,56</t>
+          <t>4,56; 94,14</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 60,99</t>
+          <t>-17,76; 56,22</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>23,06; 121,51</t>
+          <t>23,73; 122,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6,71; 98,53</t>
+          <t>10,29; 97,5</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>8,21</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,12</t>
+          <t>9,41</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>8,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,79</t>
+          <t>4,51; 8,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9,31; 13,95</t>
+          <t>9,56; 13,83</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 9,32</t>
+          <t>5,74; 10,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,64</t>
+          <t>1,13; 4,52</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,25</t>
+          <t>4,79; 8,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,32</t>
+          <t>7,85; 11,11</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,03</t>
+          <t>3,13; 6,01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>7,74; 10,4</t>
+          <t>7,65; 10,47</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,17</t>
+          <t>7,39; 10,08</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>19,95; 44,57</t>
+          <t>20,89; 44,31</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>42,39; 70,41</t>
+          <t>43,26; 69,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 45,88</t>
+          <t>26,35; 51,61</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,66; 41,89</t>
+          <t>8,78; 40,5</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>37,88; 74,24</t>
+          <t>37,72; 74,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>38,03; 90,89</t>
+          <t>60,07; 98,95</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,75; 37,94</t>
+          <t>18,68; 38,51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>45,08; 65,78</t>
+          <t>45,23; 66,67</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>23,37; 56,89</t>
+          <t>43,22; 64,26</t>
         </is>
       </c>
     </row>
